--- a/Call47/47CallParam.xlsx
+++ b/Call47/47CallParam.xlsx
@@ -50,8 +50,7 @@
     <t>进入起付线金额</t>
   </si>
   <si>
-    <t>基本医疗统筹支付
-金额</t>
+    <t>基本医疗统筹支付金额</t>
   </si>
   <si>
     <t>大额医疗支付金额</t>
